--- a/static/data/exports/Retro_DL_AE_2013.xlsx
+++ b/static/data/exports/Retro_DL_AE_2013.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -883,7 +883,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P74" t="n">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P87" t="n">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P97" t="n">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -8827,20 +8827,20 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1498042</v>
+        <v>1498041</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Meenu</t>
+          <t>Renu Bharti</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BJDI</t>
+          <t>RVNP</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>16298</v>
+        <v>16222</v>
       </c>
       <c r="E114" t="n">
         <v>193</v>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Meenu</t>
+          <t>Renu Bharti</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>BJDI</t>
+          <t>RVNP</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8879,11 +8879,11 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="Q114" t="b">
         <v>0</v>
@@ -8902,20 +8902,20 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1498041</v>
+        <v>1498042</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Renu Bharti</t>
+          <t>Meenu</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>RVNP</t>
+          <t>BJDI</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>16222</v>
+        <v>16298</v>
       </c>
       <c r="E115" t="n">
         <v>193</v>
@@ -8939,12 +8939,12 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Renu Bharti</t>
+          <t>Meenu</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>RVNP</t>
+          <t>BJDI</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8954,11 +8954,11 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="Q115" t="b">
         <v>0</v>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P116" t="n">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P119" t="n">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P134" t="n">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P135" t="n">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P137" t="n">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P152" t="n">
@@ -11765,7 +11765,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P154" t="n">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P155" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P157" t="n">
@@ -12140,7 +12140,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P158" t="n">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P160" t="n">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P161" t="n">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P163" t="n">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P165" t="n">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P167" t="n">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P168" t="n">
@@ -12952,7 +12952,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P169" t="n">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P171" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P172" t="n">
@@ -13239,7 +13239,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P174" t="n">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P175" t="n">
@@ -13464,7 +13464,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P180" t="n">
@@ -13826,7 +13826,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P181" t="n">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P183" t="n">
@@ -14113,7 +14113,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P187" t="n">
@@ -14338,7 +14338,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P188" t="n">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P189" t="n">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P190" t="n">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P191" t="n">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P192" t="n">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P193" t="n">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P194" t="n">
@@ -14863,7 +14863,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P195" t="n">
@@ -14938,7 +14938,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P196" t="n">
@@ -15075,7 +15075,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P199" t="n">
@@ -15225,7 +15225,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P201" t="n">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P202" t="n">
@@ -15450,7 +15450,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P203" t="n">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P204" t="n">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P205" t="n">
@@ -15675,7 +15675,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P206" t="n">
@@ -15698,20 +15698,20 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1498135</v>
+        <v>1498134</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Iliyash</t>
+          <t>Sunder Singh Khari</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>IBSP</t>
+          <t>RKSP</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>16311</v>
+        <v>16279</v>
       </c>
       <c r="E207" t="n">
         <v>74</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Iliyash</t>
+          <t>Sunder Singh Khari</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>IBSP</t>
+          <t>RKSP</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15750,11 +15750,11 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P207" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q207" t="b">
         <v>0</v>
@@ -15773,20 +15773,20 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1498134</v>
+        <v>1498135</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Sunder Singh Khari</t>
+          <t>Iliyash</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>RKSP</t>
+          <t>IBSP</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>16279</v>
+        <v>16311</v>
       </c>
       <c r="E208" t="n">
         <v>74</v>
@@ -15810,12 +15810,12 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Sunder Singh Khari</t>
+          <t>Iliyash</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>RKSP</t>
+          <t>IBSP</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15825,11 +15825,11 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P208" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q208" t="b">
         <v>0</v>
@@ -15900,7 +15900,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P209" t="n">
@@ -15975,7 +15975,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P210" t="n">
@@ -16050,7 +16050,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P211" t="n">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P212" t="n">
@@ -16200,7 +16200,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P214" t="n">
@@ -16350,7 +16350,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P215" t="n">
@@ -16487,7 +16487,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P217" t="n">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P218" t="n">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P219" t="n">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P220" t="n">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P221" t="n">
@@ -16862,7 +16862,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P222" t="n">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P223" t="n">
@@ -17012,7 +17012,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P224" t="n">
@@ -17087,7 +17087,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P225" t="n">
@@ -17162,7 +17162,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P226" t="n">
@@ -17237,7 +17237,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P227" t="n">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P229" t="n">
@@ -17449,7 +17449,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P230" t="n">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P232" t="n">
@@ -17674,7 +17674,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P233" t="n">
@@ -17749,7 +17749,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P234" t="n">
@@ -17824,7 +17824,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P235" t="n">
@@ -17899,7 +17899,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P236" t="n">
@@ -17974,7 +17974,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P237" t="n">
@@ -18049,7 +18049,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P238" t="n">
@@ -18124,7 +18124,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P239" t="n">
@@ -18199,7 +18199,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P240" t="n">
@@ -18274,7 +18274,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -18411,7 +18411,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P243" t="n">
@@ -18486,7 +18486,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P244" t="n">
@@ -18561,7 +18561,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P245" t="n">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P246" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P247" t="n">
@@ -18786,7 +18786,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P248" t="n">
@@ -18861,7 +18861,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P249" t="n">
@@ -18936,7 +18936,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P250" t="n">
@@ -19011,7 +19011,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P251" t="n">
@@ -19086,7 +19086,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P252" t="n">
@@ -19161,7 +19161,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P253" t="n">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P254" t="n">
@@ -19311,7 +19311,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P255" t="n">
@@ -19448,7 +19448,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P257" t="n">
@@ -19523,7 +19523,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P258" t="n">
@@ -19598,7 +19598,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P259" t="n">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P260" t="n">
@@ -19748,7 +19748,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P261" t="n">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P262" t="n">
@@ -19898,7 +19898,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P263" t="n">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P264" t="n">
@@ -20048,7 +20048,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P265" t="n">
@@ -20123,7 +20123,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P266" t="n">
@@ -20198,7 +20198,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P267" t="n">
@@ -20273,7 +20273,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P268" t="n">
@@ -20348,7 +20348,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P269" t="n">
@@ -20423,7 +20423,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P270" t="n">
@@ -20498,7 +20498,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P271" t="n">
@@ -20635,7 +20635,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P273" t="n">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P274" t="n">
@@ -20785,7 +20785,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P275" t="n">
@@ -20860,7 +20860,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P276" t="n">
@@ -20935,7 +20935,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P277" t="n">
@@ -21010,7 +21010,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P278" t="n">
@@ -21085,7 +21085,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P279" t="n">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P280" t="n">
@@ -21235,7 +21235,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P281" t="n">
@@ -21310,7 +21310,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P282" t="n">
@@ -21385,7 +21385,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P283" t="n">
@@ -21460,7 +21460,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P284" t="n">
@@ -21535,7 +21535,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P285" t="n">
@@ -21610,7 +21610,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P286" t="n">
@@ -21685,7 +21685,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P287" t="n">
@@ -21760,7 +21760,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P288" t="n">
@@ -21835,7 +21835,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P289" t="n">
@@ -21910,7 +21910,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P290" t="n">
@@ -21985,7 +21985,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P291" t="n">
@@ -22122,7 +22122,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P293" t="n">
@@ -22197,7 +22197,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P294" t="n">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P295" t="n">
@@ -22347,7 +22347,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P296" t="n">
@@ -22422,7 +22422,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P297" t="n">
@@ -22497,7 +22497,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P298" t="n">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P299" t="n">
@@ -22647,7 +22647,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P300" t="n">
@@ -22722,7 +22722,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P301" t="n">
@@ -22797,7 +22797,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P302" t="n">
@@ -22872,7 +22872,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P303" t="n">
@@ -22947,7 +22947,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P304" t="n">
@@ -23022,7 +23022,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P305" t="n">
@@ -23097,7 +23097,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P306" t="n">
@@ -23172,7 +23172,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P307" t="n">
@@ -23309,7 +23309,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P309" t="n">
@@ -23384,7 +23384,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P310" t="n">
@@ -23459,7 +23459,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P311" t="n">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P312" t="n">
@@ -23609,7 +23609,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P314" t="n">
@@ -23759,7 +23759,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P315" t="n">
@@ -23834,7 +23834,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P316" t="n">
@@ -23909,7 +23909,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -24046,7 +24046,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P319" t="n">
@@ -24121,7 +24121,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P320" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P321" t="n">
@@ -24271,7 +24271,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P322" t="n">
@@ -24346,7 +24346,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P323" t="n">
@@ -24483,7 +24483,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P325" t="n">
@@ -24558,7 +24558,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P326" t="n">
@@ -24633,7 +24633,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P327" t="n">
@@ -24708,7 +24708,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P328" t="n">
@@ -24783,7 +24783,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P329" t="n">
@@ -24858,7 +24858,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P330" t="n">
@@ -24933,7 +24933,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P331" t="n">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P332" t="n">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P333" t="n">
@@ -25158,7 +25158,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P334" t="n">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P335" t="n">
@@ -25308,7 +25308,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P336" t="n">
@@ -25445,7 +25445,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P338" t="n">
@@ -25520,7 +25520,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P339" t="n">
@@ -25595,7 +25595,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P340" t="n">
@@ -25670,7 +25670,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P341" t="n">
@@ -25745,7 +25745,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P342" t="n">
@@ -25820,7 +25820,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P343" t="n">
@@ -25895,7 +25895,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P344" t="n">
@@ -25970,7 +25970,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P345" t="n">
@@ -26045,7 +26045,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P346" t="n">
@@ -26182,7 +26182,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P348" t="n">
@@ -26257,7 +26257,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P349" t="n">
@@ -26332,7 +26332,7 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P350" t="n">
@@ -26407,7 +26407,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P351" t="n">
@@ -26482,7 +26482,7 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P352" t="n">
@@ -26557,7 +26557,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P353" t="n">
@@ -26632,7 +26632,7 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P354" t="n">
@@ -26707,7 +26707,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P355" t="n">
@@ -26782,7 +26782,7 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P356" t="n">
@@ -26857,7 +26857,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P357" t="n">
@@ -26932,7 +26932,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P358" t="n">
@@ -27069,7 +27069,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P360" t="n">
@@ -27144,7 +27144,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P361" t="n">
@@ -27219,7 +27219,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P362" t="n">
@@ -27294,7 +27294,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P363" t="n">
@@ -27369,7 +27369,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P364" t="n">
@@ -27506,7 +27506,7 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P366" t="n">
@@ -27581,7 +27581,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P367" t="n">
@@ -27656,7 +27656,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P368" t="n">
@@ -27731,7 +27731,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P369" t="n">
@@ -27806,7 +27806,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P370" t="n">
@@ -27881,7 +27881,7 @@
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P371" t="n">
@@ -27956,7 +27956,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P372" t="n">
@@ -28031,7 +28031,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P373" t="n">
@@ -28106,7 +28106,7 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P374" t="n">
@@ -28181,7 +28181,7 @@
       </c>
       <c r="O375" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P375" t="n">
@@ -28256,7 +28256,7 @@
       </c>
       <c r="O376" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P376" t="n">
@@ -28331,7 +28331,7 @@
       </c>
       <c r="O377" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P377" t="n">
@@ -28468,7 +28468,7 @@
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P379" t="n">
@@ -28543,7 +28543,7 @@
       </c>
       <c r="O380" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P380" t="n">
@@ -28618,7 +28618,7 @@
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P381" t="n">
@@ -28693,7 +28693,7 @@
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P382" t="n">
@@ -28768,7 +28768,7 @@
       </c>
       <c r="O383" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P383" t="n">
@@ -28843,7 +28843,7 @@
       </c>
       <c r="O384" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P384" t="n">
@@ -28918,7 +28918,7 @@
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P385" t="n">
@@ -28993,7 +28993,7 @@
       </c>
       <c r="O386" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P386" t="n">
@@ -29068,7 +29068,7 @@
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P387" t="n">
@@ -29143,7 +29143,7 @@
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P388" t="n">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="O390" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P390" t="n">
@@ -29355,7 +29355,7 @@
       </c>
       <c r="O391" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P391" t="n">
@@ -29430,7 +29430,7 @@
       </c>
       <c r="O392" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P392" t="n">
@@ -29505,7 +29505,7 @@
       </c>
       <c r="O393" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P393" t="n">
@@ -29580,7 +29580,7 @@
       </c>
       <c r="O394" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P394" t="n">
@@ -29655,7 +29655,7 @@
       </c>
       <c r="O395" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P395" t="n">
@@ -29730,7 +29730,7 @@
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P396" t="n">
@@ -29805,7 +29805,7 @@
       </c>
       <c r="O397" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P397" t="n">
@@ -29880,7 +29880,7 @@
       </c>
       <c r="O398" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P398" t="n">
@@ -29955,7 +29955,7 @@
       </c>
       <c r="O399" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P399" t="n">
@@ -30030,7 +30030,7 @@
       </c>
       <c r="O400" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P400" t="n">
@@ -30167,7 +30167,7 @@
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P402" t="n">
@@ -30242,7 +30242,7 @@
       </c>
       <c r="O403" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P403" t="n">
@@ -30317,7 +30317,7 @@
       </c>
       <c r="O404" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P404" t="n">
@@ -30392,7 +30392,7 @@
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P405" t="n">
@@ -30467,7 +30467,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P406" t="n">
@@ -30542,7 +30542,7 @@
       </c>
       <c r="O407" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P407" t="n">
@@ -30617,7 +30617,7 @@
       </c>
       <c r="O408" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P408" t="n">
@@ -30692,7 +30692,7 @@
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P409" t="n">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P410" t="n">
@@ -30842,7 +30842,7 @@
       </c>
       <c r="O411" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P411" t="n">
@@ -30917,7 +30917,7 @@
       </c>
       <c r="O412" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P412" t="n">
@@ -31011,11 +31011,11 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>16243</v>
+        <v>16525</v>
       </c>
       <c r="E414" t="n">
         <v>684</v>
@@ -31054,7 +31054,7 @@
       </c>
       <c r="O414" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P414" t="n">
@@ -31129,7 +31129,7 @@
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P415" t="n">
@@ -31204,7 +31204,7 @@
       </c>
       <c r="O416" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P416" t="n">
@@ -31279,7 +31279,7 @@
       </c>
       <c r="O417" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P417" t="n">
@@ -31354,7 +31354,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P418" t="n">
@@ -31429,7 +31429,7 @@
       </c>
       <c r="O419" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P419" t="n">
@@ -31504,7 +31504,7 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P420" t="n">
@@ -31579,7 +31579,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P421" t="n">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="O422" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P422" t="n">
@@ -31729,7 +31729,7 @@
       </c>
       <c r="O423" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P423" t="n">
@@ -31866,7 +31866,7 @@
       </c>
       <c r="O425" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P425" t="n">
@@ -31941,7 +31941,7 @@
       </c>
       <c r="O426" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P426" t="n">
@@ -32016,7 +32016,7 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P427" t="n">
@@ -32091,7 +32091,7 @@
       </c>
       <c r="O428" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P428" t="n">
@@ -32166,7 +32166,7 @@
       </c>
       <c r="O429" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P429" t="n">
@@ -32241,7 +32241,7 @@
       </c>
       <c r="O430" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P430" t="n">
@@ -32316,7 +32316,7 @@
       </c>
       <c r="O431" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P431" t="n">
@@ -32391,7 +32391,7 @@
       </c>
       <c r="O432" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P432" t="n">
@@ -32466,7 +32466,7 @@
       </c>
       <c r="O433" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P433" t="n">
@@ -32541,7 +32541,7 @@
       </c>
       <c r="O434" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P434" t="n">
@@ -32616,7 +32616,7 @@
       </c>
       <c r="O435" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P435" t="n">
@@ -32691,7 +32691,7 @@
       </c>
       <c r="O436" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P436" t="n">
@@ -32766,7 +32766,7 @@
       </c>
       <c r="O437" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P437" t="n">
@@ -32841,7 +32841,7 @@
       </c>
       <c r="O438" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P438" t="n">
@@ -32916,7 +32916,7 @@
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P439" t="n">
@@ -32991,7 +32991,7 @@
       </c>
       <c r="O440" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P440" t="n">
@@ -33066,7 +33066,7 @@
       </c>
       <c r="O441" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P441" t="n">
@@ -33141,7 +33141,7 @@
       </c>
       <c r="O442" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P442" t="n">
@@ -33216,7 +33216,7 @@
       </c>
       <c r="O443" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P443" t="n">
@@ -33353,7 +33353,7 @@
       </c>
       <c r="O445" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P445" t="n">
@@ -33428,7 +33428,7 @@
       </c>
       <c r="O446" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P446" t="n">
@@ -33503,7 +33503,7 @@
       </c>
       <c r="O447" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P447" t="n">
@@ -33578,7 +33578,7 @@
       </c>
       <c r="O448" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P448" t="n">
@@ -33653,7 +33653,7 @@
       </c>
       <c r="O449" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P449" t="n">
@@ -33728,7 +33728,7 @@
       </c>
       <c r="O450" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P450" t="n">
@@ -33803,7 +33803,7 @@
       </c>
       <c r="O451" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P451" t="n">
@@ -33878,7 +33878,7 @@
       </c>
       <c r="O452" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P452" t="n">
@@ -33953,7 +33953,7 @@
       </c>
       <c r="O453" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P453" t="n">
@@ -34028,7 +34028,7 @@
       </c>
       <c r="O454" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P454" t="n">
@@ -34165,7 +34165,7 @@
       </c>
       <c r="O456" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P456" t="n">
@@ -34240,7 +34240,7 @@
       </c>
       <c r="O457" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P457" t="n">
@@ -34315,7 +34315,7 @@
       </c>
       <c r="O458" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P458" t="n">
@@ -34390,7 +34390,7 @@
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P459" t="n">
@@ -34465,7 +34465,7 @@
       </c>
       <c r="O460" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P460" t="n">
@@ -34540,7 +34540,7 @@
       </c>
       <c r="O461" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P461" t="n">
@@ -34615,7 +34615,7 @@
       </c>
       <c r="O462" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P462" t="n">
@@ -34690,7 +34690,7 @@
       </c>
       <c r="O463" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P463" t="n">
@@ -34765,7 +34765,7 @@
       </c>
       <c r="O464" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P464" t="n">
@@ -34902,7 +34902,7 @@
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P466" t="n">
@@ -34977,7 +34977,7 @@
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P467" t="n">
@@ -35052,7 +35052,7 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P468" t="n">
@@ -35127,7 +35127,7 @@
       </c>
       <c r="O469" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P469" t="n">
@@ -35202,7 +35202,7 @@
       </c>
       <c r="O470" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P470" t="n">
@@ -35277,7 +35277,7 @@
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P471" t="n">
@@ -35352,7 +35352,7 @@
       </c>
       <c r="O472" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P472" t="n">
@@ -35427,7 +35427,7 @@
       </c>
       <c r="O473" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P473" t="n">
@@ -35502,7 +35502,7 @@
       </c>
       <c r="O474" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P474" t="n">
@@ -35639,7 +35639,7 @@
       </c>
       <c r="O476" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P476" t="n">
@@ -35714,7 +35714,7 @@
       </c>
       <c r="O477" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P477" t="n">
@@ -35789,7 +35789,7 @@
       </c>
       <c r="O478" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P478" t="n">
@@ -35864,7 +35864,7 @@
       </c>
       <c r="O479" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P479" t="n">
@@ -35939,7 +35939,7 @@
       </c>
       <c r="O480" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P480" t="n">
@@ -36014,7 +36014,7 @@
       </c>
       <c r="O481" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P481" t="n">
@@ -36089,7 +36089,7 @@
       </c>
       <c r="O482" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P482" t="n">
@@ -36164,7 +36164,7 @@
       </c>
       <c r="O483" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P483" t="n">
@@ -36239,7 +36239,7 @@
       </c>
       <c r="O484" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P484" t="n">
@@ -36314,7 +36314,7 @@
       </c>
       <c r="O485" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P485" t="n">
@@ -36389,7 +36389,7 @@
       </c>
       <c r="O486" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P486" t="n">
@@ -36464,7 +36464,7 @@
       </c>
       <c r="O487" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P487" t="n">
@@ -36601,7 +36601,7 @@
       </c>
       <c r="O489" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P489" t="n">
@@ -36676,7 +36676,7 @@
       </c>
       <c r="O490" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P490" t="n">
@@ -36751,7 +36751,7 @@
       </c>
       <c r="O491" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P491" t="n">
@@ -36826,7 +36826,7 @@
       </c>
       <c r="O492" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P492" t="n">
@@ -36901,7 +36901,7 @@
       </c>
       <c r="O493" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P493" t="n">
@@ -36976,7 +36976,7 @@
       </c>
       <c r="O494" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P494" t="n">
@@ -37051,7 +37051,7 @@
       </c>
       <c r="O495" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P495" t="n">
@@ -37126,7 +37126,7 @@
       </c>
       <c r="O496" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P496" t="n">
@@ -37201,7 +37201,7 @@
       </c>
       <c r="O497" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P497" t="n">
@@ -37276,7 +37276,7 @@
       </c>
       <c r="O498" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P498" t="n">
@@ -37351,7 +37351,7 @@
       </c>
       <c r="O499" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P499" t="n">
@@ -37426,7 +37426,7 @@
       </c>
       <c r="O500" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P500" t="n">
@@ -37501,7 +37501,7 @@
       </c>
       <c r="O501" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P501" t="n">
@@ -37576,7 +37576,7 @@
       </c>
       <c r="O502" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P502" t="n">
@@ -37651,7 +37651,7 @@
       </c>
       <c r="O503" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P503" t="n">
@@ -37788,7 +37788,7 @@
       </c>
       <c r="O505" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P505" t="n">
@@ -37863,7 +37863,7 @@
       </c>
       <c r="O506" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P506" t="n">
@@ -37938,7 +37938,7 @@
       </c>
       <c r="O507" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P507" t="n">
@@ -38013,7 +38013,7 @@
       </c>
       <c r="O508" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P508" t="n">
@@ -38088,7 +38088,7 @@
       </c>
       <c r="O509" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P509" t="n">
@@ -38163,7 +38163,7 @@
       </c>
       <c r="O510" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P510" t="n">
@@ -38238,7 +38238,7 @@
       </c>
       <c r="O511" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P511" t="n">
@@ -38261,11 +38261,11 @@
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>1498439</v>
+        <v>1498440</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Asad Miyan</t>
+          <t>Anand Kumar Rai</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="K512" t="inlineStr">
         <is>
-          <t>Asad Miyan</t>
+          <t>Anand Kumar Rai</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
@@ -38313,11 +38313,11 @@
       </c>
       <c r="O512" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P512" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="Q512" t="b">
         <v>0</v>
@@ -38336,11 +38336,11 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>1498440</v>
+        <v>1498439</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Anand Kumar Rai</t>
+          <t>Asad Miyan</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -38373,7 +38373,7 @@
       </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t>Anand Kumar Rai</t>
+          <t>Asad Miyan</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
@@ -38388,11 +38388,11 @@
       </c>
       <c r="O513" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P513" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="Q513" t="b">
         <v>0</v>
@@ -38463,7 +38463,7 @@
       </c>
       <c r="O514" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P514" t="n">
@@ -38538,7 +38538,7 @@
       </c>
       <c r="O515" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P515" t="n">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="O516" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P516" t="n">
@@ -38688,7 +38688,7 @@
       </c>
       <c r="O517" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P517" t="n">
@@ -38763,7 +38763,7 @@
       </c>
       <c r="O518" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P518" t="n">
@@ -38838,7 +38838,7 @@
       </c>
       <c r="O519" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P519" t="n">
@@ -38913,7 +38913,7 @@
       </c>
       <c r="O520" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P520" t="n">
@@ -38988,7 +38988,7 @@
       </c>
       <c r="O521" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P521" t="n">
@@ -39063,7 +39063,7 @@
       </c>
       <c r="O522" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P522" t="n">
@@ -39200,7 +39200,7 @@
       </c>
       <c r="O524" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P524" t="n">
@@ -39275,7 +39275,7 @@
       </c>
       <c r="O525" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P525" t="n">
@@ -39350,7 +39350,7 @@
       </c>
       <c r="O526" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P526" t="n">
@@ -39425,7 +39425,7 @@
       </c>
       <c r="O527" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P527" t="n">
@@ -39500,7 +39500,7 @@
       </c>
       <c r="O528" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P528" t="n">
@@ -39575,7 +39575,7 @@
       </c>
       <c r="O529" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P529" t="n">
@@ -39650,7 +39650,7 @@
       </c>
       <c r="O530" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P530" t="n">
@@ -39725,7 +39725,7 @@
       </c>
       <c r="O531" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P531" t="n">
@@ -39800,7 +39800,7 @@
       </c>
       <c r="O532" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P532" t="n">
@@ -39937,7 +39937,7 @@
       </c>
       <c r="O534" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P534" t="n">
@@ -40012,7 +40012,7 @@
       </c>
       <c r="O535" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P535" t="n">
@@ -40087,7 +40087,7 @@
       </c>
       <c r="O536" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P536" t="n">
@@ -40162,7 +40162,7 @@
       </c>
       <c r="O537" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P537" t="n">
@@ -40237,7 +40237,7 @@
       </c>
       <c r="O538" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P538" t="n">
@@ -40312,7 +40312,7 @@
       </c>
       <c r="O539" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P539" t="n">
@@ -40387,7 +40387,7 @@
       </c>
       <c r="O540" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P540" t="n">
@@ -40462,7 +40462,7 @@
       </c>
       <c r="O541" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P541" t="n">
@@ -40537,7 +40537,7 @@
       </c>
       <c r="O542" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P542" t="n">
@@ -40612,7 +40612,7 @@
       </c>
       <c r="O543" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P543" t="n">
@@ -40749,7 +40749,7 @@
       </c>
       <c r="O545" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P545" t="n">
@@ -40824,7 +40824,7 @@
       </c>
       <c r="O546" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P546" t="n">
@@ -40899,7 +40899,7 @@
       </c>
       <c r="O547" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P547" t="n">
@@ -40974,7 +40974,7 @@
       </c>
       <c r="O548" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P548" t="n">
@@ -41049,7 +41049,7 @@
       </c>
       <c r="O549" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P549" t="n">
@@ -41124,7 +41124,7 @@
       </c>
       <c r="O550" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P550" t="n">
@@ -41199,7 +41199,7 @@
       </c>
       <c r="O551" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P551" t="n">
@@ -41274,7 +41274,7 @@
       </c>
       <c r="O552" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P552" t="n">
@@ -41349,7 +41349,7 @@
       </c>
       <c r="O553" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P553" t="n">
@@ -41424,7 +41424,7 @@
       </c>
       <c r="O554" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P554" t="n">
@@ -41499,7 +41499,7 @@
       </c>
       <c r="O555" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P555" t="n">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="O556" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P556" t="n">
@@ -41649,7 +41649,7 @@
       </c>
       <c r="O557" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P557" t="n">
@@ -41724,7 +41724,7 @@
       </c>
       <c r="O558" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P558" t="n">
@@ -41799,7 +41799,7 @@
       </c>
       <c r="O559" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P559" t="n">
@@ -41936,7 +41936,7 @@
       </c>
       <c r="O561" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P561" t="n">
@@ -42011,7 +42011,7 @@
       </c>
       <c r="O562" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P562" t="n">
@@ -42086,7 +42086,7 @@
       </c>
       <c r="O563" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P563" t="n">
@@ -42161,7 +42161,7 @@
       </c>
       <c r="O564" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P564" t="n">
@@ -42236,7 +42236,7 @@
       </c>
       <c r="O565" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P565" t="n">
@@ -42311,7 +42311,7 @@
       </c>
       <c r="O566" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P566" t="n">
@@ -42386,7 +42386,7 @@
       </c>
       <c r="O567" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P567" t="n">
@@ -42461,7 +42461,7 @@
       </c>
       <c r="O568" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P568" t="n">
@@ -42536,7 +42536,7 @@
       </c>
       <c r="O569" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P569" t="n">
@@ -42611,7 +42611,7 @@
       </c>
       <c r="O570" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P570" t="n">
@@ -42686,7 +42686,7 @@
       </c>
       <c r="O571" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P571" t="n">
@@ -42761,7 +42761,7 @@
       </c>
       <c r="O572" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P572" t="n">
@@ -42898,7 +42898,7 @@
       </c>
       <c r="O574" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P574" t="n">
@@ -42973,7 +42973,7 @@
       </c>
       <c r="O575" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P575" t="n">
@@ -43048,7 +43048,7 @@
       </c>
       <c r="O576" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P576" t="n">
@@ -43123,7 +43123,7 @@
       </c>
       <c r="O577" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P577" t="n">
@@ -43198,7 +43198,7 @@
       </c>
       <c r="O578" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P578" t="n">
@@ -43273,7 +43273,7 @@
       </c>
       <c r="O579" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P579" t="n">
@@ -43348,7 +43348,7 @@
       </c>
       <c r="O580" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P580" t="n">
@@ -43423,7 +43423,7 @@
       </c>
       <c r="O581" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P581" t="n">
@@ -43498,7 +43498,7 @@
       </c>
       <c r="O582" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P582" t="n">
@@ -43635,7 +43635,7 @@
       </c>
       <c r="O584" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P584" t="n">
@@ -43710,7 +43710,7 @@
       </c>
       <c r="O585" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P585" t="n">
@@ -43785,7 +43785,7 @@
       </c>
       <c r="O586" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P586" t="n">
@@ -43860,7 +43860,7 @@
       </c>
       <c r="O587" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P587" t="n">
@@ -43935,7 +43935,7 @@
       </c>
       <c r="O588" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P588" t="n">
@@ -44010,7 +44010,7 @@
       </c>
       <c r="O589" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P589" t="n">
@@ -44085,7 +44085,7 @@
       </c>
       <c r="O590" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P590" t="n">
@@ -44222,7 +44222,7 @@
       </c>
       <c r="O592" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P592" t="n">
@@ -44297,7 +44297,7 @@
       </c>
       <c r="O593" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P593" t="n">
@@ -44372,7 +44372,7 @@
       </c>
       <c r="O594" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P594" t="n">
@@ -44447,7 +44447,7 @@
       </c>
       <c r="O595" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P595" t="n">
@@ -44522,7 +44522,7 @@
       </c>
       <c r="O596" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P596" t="n">
@@ -44659,7 +44659,7 @@
       </c>
       <c r="O598" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P598" t="n">
@@ -44734,7 +44734,7 @@
       </c>
       <c r="O599" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P599" t="n">
@@ -44809,7 +44809,7 @@
       </c>
       <c r="O600" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P600" t="n">
@@ -44884,7 +44884,7 @@
       </c>
       <c r="O601" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P601" t="n">
@@ -44959,7 +44959,7 @@
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P602" t="n">
@@ -45034,7 +45034,7 @@
       </c>
       <c r="O603" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P603" t="n">
@@ -45109,7 +45109,7 @@
       </c>
       <c r="O604" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P604" t="n">
@@ -45184,7 +45184,7 @@
       </c>
       <c r="O605" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P605" t="n">
@@ -45259,7 +45259,7 @@
       </c>
       <c r="O606" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P606" t="n">
@@ -45334,7 +45334,7 @@
       </c>
       <c r="O607" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P607" t="n">
@@ -45409,7 +45409,7 @@
       </c>
       <c r="O608" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P608" t="n">
@@ -45484,7 +45484,7 @@
       </c>
       <c r="O609" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P609" t="n">
@@ -45559,7 +45559,7 @@
       </c>
       <c r="O610" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P610" t="n">
@@ -45634,7 +45634,7 @@
       </c>
       <c r="O611" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P611" t="n">
@@ -45771,7 +45771,7 @@
       </c>
       <c r="O613" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P613" t="n">
@@ -45846,7 +45846,7 @@
       </c>
       <c r="O614" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P614" t="n">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="O615" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P615" t="n">
@@ -45996,7 +45996,7 @@
       </c>
       <c r="O616" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P616" t="n">
@@ -46071,7 +46071,7 @@
       </c>
       <c r="O617" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P617" t="n">
@@ -46146,7 +46146,7 @@
       </c>
       <c r="O618" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P618" t="n">
@@ -46221,7 +46221,7 @@
       </c>
       <c r="O619" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P619" t="n">
@@ -46296,7 +46296,7 @@
       </c>
       <c r="O620" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P620" t="n">
@@ -46371,7 +46371,7 @@
       </c>
       <c r="O621" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P621" t="n">
@@ -46446,7 +46446,7 @@
       </c>
       <c r="O622" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P622" t="n">
@@ -46521,7 +46521,7 @@
       </c>
       <c r="O623" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P623" t="n">
@@ -46596,7 +46596,7 @@
       </c>
       <c r="O624" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P624" t="n">
@@ -46733,7 +46733,7 @@
       </c>
       <c r="O626" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P626" t="n">
@@ -46808,7 +46808,7 @@
       </c>
       <c r="O627" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P627" t="n">
@@ -46883,7 +46883,7 @@
       </c>
       <c r="O628" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P628" t="n">
@@ -46958,7 +46958,7 @@
       </c>
       <c r="O629" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P629" t="n">
@@ -47033,7 +47033,7 @@
       </c>
       <c r="O630" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P630" t="n">
@@ -47108,7 +47108,7 @@
       </c>
       <c r="O631" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P631" t="n">
@@ -47183,7 +47183,7 @@
       </c>
       <c r="O632" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P632" t="n">
@@ -47320,7 +47320,7 @@
       </c>
       <c r="O634" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P634" t="n">
@@ -47395,7 +47395,7 @@
       </c>
       <c r="O635" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P635" t="n">
@@ -47470,7 +47470,7 @@
       </c>
       <c r="O636" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P636" t="n">
@@ -47545,7 +47545,7 @@
       </c>
       <c r="O637" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P637" t="n">
@@ -47620,7 +47620,7 @@
       </c>
       <c r="O638" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P638" t="n">
@@ -47695,7 +47695,7 @@
       </c>
       <c r="O639" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P639" t="n">
@@ -47770,7 +47770,7 @@
       </c>
       <c r="O640" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P640" t="n">
@@ -47845,7 +47845,7 @@
       </c>
       <c r="O641" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P641" t="n">
@@ -47920,7 +47920,7 @@
       </c>
       <c r="O642" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P642" t="n">
@@ -47995,7 +47995,7 @@
       </c>
       <c r="O643" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P643" t="n">
@@ -48070,7 +48070,7 @@
       </c>
       <c r="O644" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P644" t="n">
@@ -48145,7 +48145,7 @@
       </c>
       <c r="O645" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P645" t="n">
@@ -48220,7 +48220,7 @@
       </c>
       <c r="O646" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P646" t="n">
@@ -48357,7 +48357,7 @@
       </c>
       <c r="O648" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P648" t="n">
@@ -48432,7 +48432,7 @@
       </c>
       <c r="O649" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P649" t="n">
@@ -48507,7 +48507,7 @@
       </c>
       <c r="O650" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P650" t="n">
@@ -48582,7 +48582,7 @@
       </c>
       <c r="O651" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P651" t="n">
@@ -48657,7 +48657,7 @@
       </c>
       <c r="O652" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P652" t="n">
@@ -48732,7 +48732,7 @@
       </c>
       <c r="O653" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P653" t="n">
@@ -48807,7 +48807,7 @@
       </c>
       <c r="O654" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P654" t="n">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="O655" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P655" t="n">
@@ -48957,7 +48957,7 @@
       </c>
       <c r="O656" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P656" t="n">
@@ -49032,7 +49032,7 @@
       </c>
       <c r="O657" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P657" t="n">
@@ -49107,7 +49107,7 @@
       </c>
       <c r="O658" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P658" t="n">
@@ -49244,7 +49244,7 @@
       </c>
       <c r="O660" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P660" t="n">
@@ -49319,7 +49319,7 @@
       </c>
       <c r="O661" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P661" t="n">
@@ -49394,7 +49394,7 @@
       </c>
       <c r="O662" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P662" t="n">
@@ -49469,7 +49469,7 @@
       </c>
       <c r="O663" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P663" t="n">
@@ -49544,7 +49544,7 @@
       </c>
       <c r="O664" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P664" t="n">
@@ -49619,7 +49619,7 @@
       </c>
       <c r="O665" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P665" t="n">
@@ -49694,7 +49694,7 @@
       </c>
       <c r="O666" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P666" t="n">
@@ -49769,7 +49769,7 @@
       </c>
       <c r="O667" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P667" t="n">
@@ -49844,7 +49844,7 @@
       </c>
       <c r="O668" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P668" t="n">
@@ -49919,7 +49919,7 @@
       </c>
       <c r="O669" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P669" t="n">
@@ -49994,7 +49994,7 @@
       </c>
       <c r="O670" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P670" t="n">
@@ -50069,7 +50069,7 @@
       </c>
       <c r="O671" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P671" t="n">
@@ -50144,7 +50144,7 @@
       </c>
       <c r="O672" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P672" t="n">
@@ -50219,7 +50219,7 @@
       </c>
       <c r="O673" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P673" t="n">
@@ -50294,7 +50294,7 @@
       </c>
       <c r="O674" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P674" t="n">
@@ -50369,7 +50369,7 @@
       </c>
       <c r="O675" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P675" t="n">
@@ -50444,7 +50444,7 @@
       </c>
       <c r="O676" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P676" t="n">
@@ -50519,7 +50519,7 @@
       </c>
       <c r="O677" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P677" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="O678" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P678" t="n">
@@ -50669,7 +50669,7 @@
       </c>
       <c r="O679" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P679" t="n">
@@ -50806,7 +50806,7 @@
       </c>
       <c r="O681" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P681" t="n">
@@ -50881,7 +50881,7 @@
       </c>
       <c r="O682" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P682" t="n">
@@ -50956,7 +50956,7 @@
       </c>
       <c r="O683" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P683" t="n">
@@ -51031,7 +51031,7 @@
       </c>
       <c r="O684" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P684" t="n">
@@ -51106,7 +51106,7 @@
       </c>
       <c r="O685" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P685" t="n">
@@ -51181,7 +51181,7 @@
       </c>
       <c r="O686" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P686" t="n">
@@ -51256,7 +51256,7 @@
       </c>
       <c r="O687" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P687" t="n">
@@ -51331,7 +51331,7 @@
       </c>
       <c r="O688" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P688" t="n">
@@ -51406,7 +51406,7 @@
       </c>
       <c r="O689" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P689" t="n">
@@ -51481,7 +51481,7 @@
       </c>
       <c r="O690" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P690" t="n">
@@ -51556,7 +51556,7 @@
       </c>
       <c r="O691" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P691" t="n">
@@ -51631,7 +51631,7 @@
       </c>
       <c r="O692" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P692" t="n">
@@ -51706,7 +51706,7 @@
       </c>
       <c r="O693" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P693" t="n">
@@ -51843,7 +51843,7 @@
       </c>
       <c r="O695" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P695" t="n">
@@ -51918,7 +51918,7 @@
       </c>
       <c r="O696" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P696" t="n">
@@ -51993,7 +51993,7 @@
       </c>
       <c r="O697" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P697" t="n">
@@ -52068,7 +52068,7 @@
       </c>
       <c r="O698" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P698" t="n">
@@ -52143,7 +52143,7 @@
       </c>
       <c r="O699" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P699" t="n">
@@ -52218,7 +52218,7 @@
       </c>
       <c r="O700" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P700" t="n">
@@ -52293,7 +52293,7 @@
       </c>
       <c r="O701" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P701" t="n">
@@ -52368,7 +52368,7 @@
       </c>
       <c r="O702" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P702" t="n">
@@ -52443,7 +52443,7 @@
       </c>
       <c r="O703" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P703" t="n">
@@ -52518,7 +52518,7 @@
       </c>
       <c r="O704" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P704" t="n">
@@ -52593,7 +52593,7 @@
       </c>
       <c r="O705" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P705" t="n">
@@ -52730,7 +52730,7 @@
       </c>
       <c r="O707" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P707" t="n">
@@ -52805,7 +52805,7 @@
       </c>
       <c r="O708" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P708" t="n">
@@ -52880,7 +52880,7 @@
       </c>
       <c r="O709" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P709" t="n">
@@ -52955,7 +52955,7 @@
       </c>
       <c r="O710" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P710" t="n">
@@ -53030,7 +53030,7 @@
       </c>
       <c r="O711" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P711" t="n">
@@ -53105,7 +53105,7 @@
       </c>
       <c r="O712" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P712" t="n">
@@ -53180,7 +53180,7 @@
       </c>
       <c r="O713" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P713" t="n">
@@ -53255,7 +53255,7 @@
       </c>
       <c r="O714" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P714" t="n">
@@ -53330,7 +53330,7 @@
       </c>
       <c r="O715" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P715" t="n">
@@ -53467,7 +53467,7 @@
       </c>
       <c r="O717" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P717" t="n">
@@ -53542,7 +53542,7 @@
       </c>
       <c r="O718" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P718" t="n">
@@ -53617,7 +53617,7 @@
       </c>
       <c r="O719" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P719" t="n">
@@ -53692,7 +53692,7 @@
       </c>
       <c r="O720" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P720" t="n">
@@ -53767,7 +53767,7 @@
       </c>
       <c r="O721" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P721" t="n">
@@ -53842,7 +53842,7 @@
       </c>
       <c r="O722" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P722" t="n">
@@ -53917,7 +53917,7 @@
       </c>
       <c r="O723" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P723" t="n">
@@ -53992,7 +53992,7 @@
       </c>
       <c r="O724" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P724" t="n">
@@ -54067,7 +54067,7 @@
       </c>
       <c r="O725" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P725" t="n">
@@ -54142,7 +54142,7 @@
       </c>
       <c r="O726" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P726" t="n">
@@ -54217,7 +54217,7 @@
       </c>
       <c r="O727" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P727" t="n">
@@ -54292,7 +54292,7 @@
       </c>
       <c r="O728" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P728" t="n">
@@ -54429,7 +54429,7 @@
       </c>
       <c r="O730" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P730" t="n">
@@ -54504,7 +54504,7 @@
       </c>
       <c r="O731" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P731" t="n">
@@ -54579,7 +54579,7 @@
       </c>
       <c r="O732" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P732" t="n">
@@ -54654,7 +54654,7 @@
       </c>
       <c r="O733" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P733" t="n">
@@ -54729,7 +54729,7 @@
       </c>
       <c r="O734" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P734" t="n">
@@ -54804,7 +54804,7 @@
       </c>
       <c r="O735" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P735" t="n">
@@ -54879,7 +54879,7 @@
       </c>
       <c r="O736" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P736" t="n">
@@ -54954,7 +54954,7 @@
       </c>
       <c r="O737" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P737" t="n">
@@ -55029,7 +55029,7 @@
       </c>
       <c r="O738" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P738" t="n">
@@ -55104,7 +55104,7 @@
       </c>
       <c r="O739" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P739" t="n">
@@ -55179,7 +55179,7 @@
       </c>
       <c r="O740" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P740" t="n">
@@ -55254,7 +55254,7 @@
       </c>
       <c r="O741" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P741" t="n">
@@ -55329,7 +55329,7 @@
       </c>
       <c r="O742" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P742" t="n">
@@ -55466,7 +55466,7 @@
       </c>
       <c r="O744" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P744" t="n">
@@ -55541,7 +55541,7 @@
       </c>
       <c r="O745" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P745" t="n">
@@ -55616,7 +55616,7 @@
       </c>
       <c r="O746" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P746" t="n">
@@ -55691,7 +55691,7 @@
       </c>
       <c r="O747" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P747" t="n">
@@ -55766,7 +55766,7 @@
       </c>
       <c r="O748" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P748" t="n">
@@ -55841,7 +55841,7 @@
       </c>
       <c r="O749" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P749" t="n">
@@ -55916,7 +55916,7 @@
       </c>
       <c r="O750" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P750" t="n">
@@ -56053,7 +56053,7 @@
       </c>
       <c r="O752" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P752" t="n">
@@ -56128,7 +56128,7 @@
       </c>
       <c r="O753" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P753" t="n">
@@ -56203,7 +56203,7 @@
       </c>
       <c r="O754" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P754" t="n">
@@ -56278,7 +56278,7 @@
       </c>
       <c r="O755" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P755" t="n">
@@ -56353,7 +56353,7 @@
       </c>
       <c r="O756" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P756" t="n">
@@ -56428,7 +56428,7 @@
       </c>
       <c r="O757" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P757" t="n">
@@ -56503,7 +56503,7 @@
       </c>
       <c r="O758" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P758" t="n">
@@ -56578,7 +56578,7 @@
       </c>
       <c r="O759" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P759" t="n">
@@ -56653,7 +56653,7 @@
       </c>
       <c r="O760" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P760" t="n">
@@ -56790,7 +56790,7 @@
       </c>
       <c r="O762" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P762" t="n">
@@ -56865,7 +56865,7 @@
       </c>
       <c r="O763" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P763" t="n">
@@ -56940,7 +56940,7 @@
       </c>
       <c r="O764" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P764" t="n">
@@ -57015,7 +57015,7 @@
       </c>
       <c r="O765" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P765" t="n">
@@ -57090,7 +57090,7 @@
       </c>
       <c r="O766" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P766" t="n">
@@ -57165,7 +57165,7 @@
       </c>
       <c r="O767" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P767" t="n">
@@ -57240,7 +57240,7 @@
       </c>
       <c r="O768" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P768" t="n">
@@ -57315,7 +57315,7 @@
       </c>
       <c r="O769" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P769" t="n">
@@ -57390,7 +57390,7 @@
       </c>
       <c r="O770" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P770" t="n">
@@ -57465,7 +57465,7 @@
       </c>
       <c r="O771" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P771" t="n">
@@ -57540,7 +57540,7 @@
       </c>
       <c r="O772" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P772" t="n">
@@ -57615,7 +57615,7 @@
       </c>
       <c r="O773" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P773" t="n">
@@ -57690,7 +57690,7 @@
       </c>
       <c r="O774" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P774" t="n">
@@ -57827,7 +57827,7 @@
       </c>
       <c r="O776" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P776" t="n">
@@ -57902,7 +57902,7 @@
       </c>
       <c r="O777" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P777" t="n">
@@ -57977,7 +57977,7 @@
       </c>
       <c r="O778" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P778" t="n">
@@ -58052,7 +58052,7 @@
       </c>
       <c r="O779" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P779" t="n">
@@ -58084,11 +58084,11 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D780" t="n">
-        <v>16243</v>
+        <v>16525</v>
       </c>
       <c r="E780" t="n">
         <v>121</v>
@@ -58127,7 +58127,7 @@
       </c>
       <c r="O780" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P780" t="n">
@@ -58202,7 +58202,7 @@
       </c>
       <c r="O781" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P781" t="n">
@@ -58277,7 +58277,7 @@
       </c>
       <c r="O782" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P782" t="n">
@@ -58352,7 +58352,7 @@
       </c>
       <c r="O783" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P783" t="n">
@@ -58427,7 +58427,7 @@
       </c>
       <c r="O784" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P784" t="n">
@@ -58502,7 +58502,7 @@
       </c>
       <c r="O785" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P785" t="n">
@@ -58639,7 +58639,7 @@
       </c>
       <c r="O787" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P787" t="n">
@@ -58714,7 +58714,7 @@
       </c>
       <c r="O788" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P788" t="n">
@@ -58789,7 +58789,7 @@
       </c>
       <c r="O789" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P789" t="n">
@@ -58864,7 +58864,7 @@
       </c>
       <c r="O790" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P790" t="n">
@@ -58939,7 +58939,7 @@
       </c>
       <c r="O791" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P791" t="n">
@@ -59014,7 +59014,7 @@
       </c>
       <c r="O792" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P792" t="n">
@@ -59089,7 +59089,7 @@
       </c>
       <c r="O793" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P793" t="n">
@@ -59164,7 +59164,7 @@
       </c>
       <c r="O794" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P794" t="n">
@@ -59239,7 +59239,7 @@
       </c>
       <c r="O795" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P795" t="n">
@@ -59314,7 +59314,7 @@
       </c>
       <c r="O796" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P796" t="n">
@@ -59389,7 +59389,7 @@
       </c>
       <c r="O797" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P797" t="n">
@@ -59526,7 +59526,7 @@
       </c>
       <c r="O799" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P799" t="n">
@@ -59601,7 +59601,7 @@
       </c>
       <c r="O800" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P800" t="n">
@@ -59676,7 +59676,7 @@
       </c>
       <c r="O801" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P801" t="n">
@@ -59751,7 +59751,7 @@
       </c>
       <c r="O802" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P802" t="n">
@@ -59826,7 +59826,7 @@
       </c>
       <c r="O803" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P803" t="n">
@@ -59901,7 +59901,7 @@
       </c>
       <c r="O804" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P804" t="n">
@@ -59976,7 +59976,7 @@
       </c>
       <c r="O805" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P805" t="n">
@@ -60051,7 +60051,7 @@
       </c>
       <c r="O806" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P806" t="n">
@@ -60126,7 +60126,7 @@
       </c>
       <c r="O807" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P807" t="n">
@@ -60201,7 +60201,7 @@
       </c>
       <c r="O808" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P808" t="n">
@@ -60276,7 +60276,7 @@
       </c>
       <c r="O809" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P809" t="n">
@@ -60413,7 +60413,7 @@
       </c>
       <c r="O811" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P811" t="n">
@@ -60488,7 +60488,7 @@
       </c>
       <c r="O812" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P812" t="n">
@@ -60563,7 +60563,7 @@
       </c>
       <c r="O813" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P813" t="n">
@@ -60638,7 +60638,7 @@
       </c>
       <c r="O814" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P814" t="n">
@@ -60713,7 +60713,7 @@
       </c>
       <c r="O815" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P815" t="n">
@@ -60788,7 +60788,7 @@
       </c>
       <c r="O816" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P816" t="n">
@@ -60863,7 +60863,7 @@
       </c>
       <c r="O817" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P817" t="n">
@@ -60938,7 +60938,7 @@
       </c>
       <c r="O818" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P818" t="n">
@@ -61075,7 +61075,7 @@
       </c>
       <c r="O820" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P820" t="n">
@@ -61150,7 +61150,7 @@
       </c>
       <c r="O821" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P821" t="n">
@@ -61225,7 +61225,7 @@
       </c>
       <c r="O822" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P822" t="n">
@@ -61300,7 +61300,7 @@
       </c>
       <c r="O823" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P823" t="n">
@@ -61375,7 +61375,7 @@
       </c>
       <c r="O824" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P824" t="n">
@@ -61450,7 +61450,7 @@
       </c>
       <c r="O825" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P825" t="n">
@@ -61525,7 +61525,7 @@
       </c>
       <c r="O826" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P826" t="n">
@@ -61600,7 +61600,7 @@
       </c>
       <c r="O827" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P827" t="n">
@@ -61675,7 +61675,7 @@
       </c>
       <c r="O828" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P828" t="n">
@@ -61750,7 +61750,7 @@
       </c>
       <c r="O829" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P829" t="n">
@@ -61825,7 +61825,7 @@
       </c>
       <c r="O830" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P830" t="n">
@@ -61900,7 +61900,7 @@
       </c>
       <c r="O831" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P831" t="n">
@@ -61975,7 +61975,7 @@
       </c>
       <c r="O832" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P832" t="n">
@@ -62050,7 +62050,7 @@
       </c>
       <c r="O833" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P833" t="n">
@@ -62125,7 +62125,7 @@
       </c>
       <c r="O834" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P834" t="n">
@@ -62200,7 +62200,7 @@
       </c>
       <c r="O835" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P835" t="n">
@@ -62275,7 +62275,7 @@
       </c>
       <c r="O836" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P836" t="n">
@@ -62412,7 +62412,7 @@
       </c>
       <c r="O838" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P838" t="n">
@@ -62487,7 +62487,7 @@
       </c>
       <c r="O839" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P839" t="n">
@@ -62562,7 +62562,7 @@
       </c>
       <c r="O840" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P840" t="n">
@@ -62637,7 +62637,7 @@
       </c>
       <c r="O841" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P841" t="n">
@@ -62712,7 +62712,7 @@
       </c>
       <c r="O842" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P842" t="n">
@@ -62787,7 +62787,7 @@
       </c>
       <c r="O843" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P843" t="n">
@@ -62862,7 +62862,7 @@
       </c>
       <c r="O844" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P844" t="n">
@@ -62937,7 +62937,7 @@
       </c>
       <c r="O845" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P845" t="n">
@@ -63074,7 +63074,7 @@
       </c>
       <c r="O847" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P847" t="n">
@@ -63149,7 +63149,7 @@
       </c>
       <c r="O848" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P848" t="n">
@@ -63224,7 +63224,7 @@
       </c>
       <c r="O849" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P849" t="n">
@@ -63299,7 +63299,7 @@
       </c>
       <c r="O850" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P850" t="n">
@@ -63374,7 +63374,7 @@
       </c>
       <c r="O851" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P851" t="n">
@@ -63449,7 +63449,7 @@
       </c>
       <c r="O852" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P852" t="n">
@@ -63524,7 +63524,7 @@
       </c>
       <c r="O853" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P853" t="n">
@@ -63599,7 +63599,7 @@
       </c>
       <c r="O854" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P854" t="n">
@@ -63674,7 +63674,7 @@
       </c>
       <c r="O855" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P855" t="n">
@@ -63749,7 +63749,7 @@
       </c>
       <c r="O856" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P856" t="n">
@@ -63824,7 +63824,7 @@
       </c>
       <c r="O857" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P857" t="n">
@@ -63899,7 +63899,7 @@
       </c>
       <c r="O858" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P858" t="n">
@@ -63974,7 +63974,7 @@
       </c>
       <c r="O859" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P859" t="n">
@@ -64111,7 +64111,7 @@
       </c>
       <c r="O861" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P861" t="n">
@@ -64186,7 +64186,7 @@
       </c>
       <c r="O862" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P862" t="n">
@@ -64261,7 +64261,7 @@
       </c>
       <c r="O863" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P863" t="n">
@@ -64336,7 +64336,7 @@
       </c>
       <c r="O864" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P864" t="n">
@@ -64359,20 +64359,20 @@
     </row>
     <row r="865">
       <c r="A865" t="n">
-        <v>1498793</v>
+        <v>1498792</v>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>Shaquib Yusufzai Khan</t>
+          <t>Kadir Ahmed</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>JD(U)</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="D865" t="n">
-        <v>16215</v>
+        <v>16337</v>
       </c>
       <c r="E865" t="n">
         <v>164</v>
@@ -64396,12 +64396,12 @@
       </c>
       <c r="K865" t="inlineStr">
         <is>
-          <t>Shaquib Yusufzai Khan</t>
+          <t>Kadir Ahmed</t>
         </is>
       </c>
       <c r="L865" t="inlineStr">
         <is>
-          <t>JD(U)</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="N865" t="inlineStr">
@@ -64411,11 +64411,11 @@
       </c>
       <c r="O865" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P865" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="Q865" t="b">
         <v>0</v>
@@ -64434,20 +64434,20 @@
     </row>
     <row r="866">
       <c r="A866" t="n">
-        <v>1498792</v>
+        <v>1498793</v>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>Kadir Ahmed</t>
+          <t>Shaquib Yusufzai Khan</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>JD(U)</t>
         </is>
       </c>
       <c r="D866" t="n">
-        <v>16337</v>
+        <v>16215</v>
       </c>
       <c r="E866" t="n">
         <v>164</v>
@@ -64471,12 +64471,12 @@
       </c>
       <c r="K866" t="inlineStr">
         <is>
-          <t>Kadir Ahmed</t>
+          <t>Shaquib Yusufzai Khan</t>
         </is>
       </c>
       <c r="L866" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>JD(U)</t>
         </is>
       </c>
       <c r="N866" t="inlineStr">
@@ -64486,11 +64486,11 @@
       </c>
       <c r="O866" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P866" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q866" t="b">
         <v>0</v>
@@ -64561,7 +64561,7 @@
       </c>
       <c r="O867" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P867" t="n">
@@ -64636,7 +64636,7 @@
       </c>
       <c r="O868" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P868" t="n">
@@ -64711,7 +64711,7 @@
       </c>
       <c r="O869" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P869" t="n">
@@ -64786,7 +64786,7 @@
       </c>
       <c r="O870" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P870" t="n">
@@ -64861,7 +64861,7 @@
       </c>
       <c r="O871" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P871" t="n">
@@ -64936,7 +64936,7 @@
       </c>
       <c r="O872" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P872" t="n">
@@ -64968,11 +64968,11 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D873" t="n">
-        <v>16243</v>
+        <v>16525</v>
       </c>
       <c r="E873" t="n">
         <v>1199</v>
@@ -65011,7 +65011,7 @@
       </c>
       <c r="O873" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P873" t="n">
@@ -65148,7 +65148,7 @@
       </c>
       <c r="O875" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P875" t="n">
@@ -65223,7 +65223,7 @@
       </c>
       <c r="O876" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P876" t="n">
@@ -65298,7 +65298,7 @@
       </c>
       <c r="O877" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P877" t="n">
@@ -65373,7 +65373,7 @@
       </c>
       <c r="O878" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P878" t="n">
@@ -65448,7 +65448,7 @@
       </c>
       <c r="O879" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P879" t="n">
@@ -65523,7 +65523,7 @@
       </c>
       <c r="O880" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P880" t="n">
@@ -65598,7 +65598,7 @@
       </c>
       <c r="O881" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P881" t="n">
